--- a/assets/elias-lab-inventory-template.xlsx
+++ b/assets/elias-lab-inventory-template.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D49"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -437,40 +437,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Rows without a name are skipped, and so are rows identical to an item already in the inventory.</v>
+        <v>Rows missing the required (first) column are skipped, and so are rows identical to an item already in the inventory.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>Glycerol stock serial numbers must be unique: a row reusing a serial that is already taken (in the inventory or earlier in the file) is skipped.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
         <v>Primers are not included: add them in the Primer Generator.</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Sheet</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Column</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Required</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Example</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Restriction Enzymes</v>
+        <v>Sheet</v>
       </c>
       <c r="B11" t="str">
-        <v>Name</v>
+        <v>Column</v>
       </c>
       <c r="C11" t="str">
-        <v>yes</v>
+        <v>Required</v>
       </c>
       <c r="D11" t="str">
-        <v>EcoRI</v>
+        <v>Example</v>
       </c>
     </row>
     <row r="12">
@@ -478,13 +469,13 @@
         <v>Restriction Enzymes</v>
       </c>
       <c r="B12" t="str">
-        <v>Supplier</v>
+        <v>Name</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="D12" t="str">
-        <v>NEB</v>
+        <v>EcoRI</v>
       </c>
     </row>
     <row r="13">
@@ -492,13 +483,13 @@
         <v>Restriction Enzymes</v>
       </c>
       <c r="B13" t="str">
-        <v>Catalog #</v>
+        <v>Supplier</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
       <c r="D13" t="str">
-        <v>R0101S</v>
+        <v>NEB</v>
       </c>
     </row>
     <row r="14">
@@ -506,13 +497,13 @@
         <v>Restriction Enzymes</v>
       </c>
       <c r="B14" t="str">
-        <v>Cut Site</v>
+        <v>Catalog #</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
       <c r="D14" t="str">
-        <v>G↓AATTC</v>
+        <v>R0101S</v>
       </c>
     </row>
     <row r="15">
@@ -520,13 +511,13 @@
         <v>Restriction Enzymes</v>
       </c>
       <c r="B15" t="str">
-        <v>Conc.</v>
+        <v>Cut Site</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>20,000 U/mL</v>
+        <v>G↓AATTC</v>
       </c>
     </row>
     <row r="16">
@@ -534,13 +525,13 @@
         <v>Restriction Enzymes</v>
       </c>
       <c r="B16" t="str">
-        <v>Qty</v>
+        <v>Conc.</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
       <c r="D16" t="str">
-        <v>3 vials</v>
+        <v>20,000 U/mL</v>
       </c>
     </row>
     <row r="17">
@@ -548,27 +539,27 @@
         <v>Restriction Enzymes</v>
       </c>
       <c r="B17" t="str">
-        <v>Storage</v>
+        <v>Qty</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
       <c r="D17" t="str">
-        <v>-20°C Box 2A</v>
+        <v>3 vials</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Plasmids</v>
+        <v>Restriction Enzymes</v>
       </c>
       <c r="B18" t="str">
-        <v>Name</v>
+        <v>Storage</v>
       </c>
       <c r="C18" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="D18" t="str">
-        <v>pUC19-HK022</v>
+        <v>-20°C Box 2A</v>
       </c>
     </row>
     <row r="19">
@@ -576,13 +567,13 @@
         <v>Plasmids</v>
       </c>
       <c r="B19" t="str">
-        <v>Backbone</v>
+        <v>Name</v>
       </c>
       <c r="C19" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="D19" t="str">
-        <v>pUC19</v>
+        <v>pUC19-HK022</v>
       </c>
     </row>
     <row r="20">
@@ -590,13 +581,13 @@
         <v>Plasmids</v>
       </c>
       <c r="B20" t="str">
-        <v>Insert</v>
+        <v>Backbone</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>HK022 integrase CDS</v>
+        <v>pUC19</v>
       </c>
     </row>
     <row r="21">
@@ -604,13 +595,13 @@
         <v>Plasmids</v>
       </c>
       <c r="B21" t="str">
-        <v>Resistance</v>
+        <v>Insert</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
       <c r="D21" t="str">
-        <v>AmpR</v>
+        <v>HK022 integrase CDS</v>
       </c>
     </row>
     <row r="22">
@@ -618,27 +609,27 @@
         <v>Plasmids</v>
       </c>
       <c r="B22" t="str">
-        <v>Location</v>
+        <v>Resistance</v>
       </c>
       <c r="C22" t="str">
         <v/>
       </c>
       <c r="D22" t="str">
-        <v>-80°C Plasmid Box 1</v>
+        <v>AmpR</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Glycerol Stocks</v>
+        <v>Plasmids</v>
       </c>
       <c r="B23" t="str">
-        <v>Strain / Name</v>
+        <v>Location</v>
       </c>
       <c r="C23" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="D23" t="str">
-        <v>HEK293-HK022-GFP</v>
+        <v>-80°C Plasmid Box 1</v>
       </c>
     </row>
     <row r="24">
@@ -646,13 +637,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B24" t="str">
-        <v>Plasmid</v>
+        <v>Serial #</v>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="D24" t="str">
-        <v>pHK022-GFP</v>
+        <v>GS-0001 (must be unique)</v>
       </c>
     </row>
     <row r="25">
@@ -660,13 +651,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B25" t="str">
-        <v>Date Prepared</v>
+        <v>Description</v>
       </c>
       <c r="C25" t="str">
         <v/>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-05</v>
+        <v>pUC19-HK022 attB, clone 3</v>
       </c>
     </row>
     <row r="26">
@@ -674,13 +665,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B26" t="str">
-        <v>Box</v>
+        <v>Resistance</v>
       </c>
       <c r="C26" t="str">
         <v/>
       </c>
       <c r="D26" t="str">
-        <v>-80°C Box G1, slot 3</v>
+        <v>AmpR</v>
       </c>
     </row>
     <row r="27">
@@ -688,200 +679,326 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B27" t="str">
-        <v>Made by</v>
+        <v>Sequenced (QC)</v>
       </c>
       <c r="C27" t="str">
         <v/>
       </c>
       <c r="D27" t="str">
-        <v>Blank = your name</v>
+        <v>Sequenced with M13F + M13R, correct</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Tissue Culture</v>
+        <v>Glycerol Stocks</v>
       </c>
       <c r="B28" t="str">
-        <v>Cell Line</v>
+        <v>Strain</v>
       </c>
       <c r="C28" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="D28" t="str">
-        <v>HEK293T</v>
+        <v>DH5α, NEB Stable, Stbl3 or other</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Tissue Culture</v>
+        <v>Glycerol Stocks</v>
       </c>
       <c r="B29" t="str">
-        <v>Passage</v>
+        <v>Freezer (-80°C)</v>
       </c>
       <c r="C29" t="str">
         <v/>
       </c>
       <c r="D29" t="str">
-        <v>P12</v>
+        <v>Freezer A</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Tissue Culture</v>
+        <v>Glycerol Stocks</v>
       </c>
       <c r="B30" t="str">
-        <v>Source</v>
+        <v>Shelf</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
       <c r="D30" t="str">
-        <v>ATCC CRL-3216</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Tissue Culture</v>
+        <v>Glycerol Stocks</v>
       </c>
       <c r="B31" t="str">
-        <v>Liquid N₂ Tank</v>
+        <v>Place on Shelf</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
       <c r="D31" t="str">
-        <v>LN2 Tank 1</v>
+        <v>Left, front</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Tissue Culture</v>
+        <v>Glycerol Stocks</v>
       </c>
       <c r="B32" t="str">
-        <v>Rack</v>
+        <v>Box</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>Rack 3</v>
+        <v>Box G1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Tissue Culture</v>
+        <v>Glycerol Stocks</v>
       </c>
       <c r="B33" t="str">
-        <v>Box</v>
+        <v>Position</v>
       </c>
       <c r="C33" t="str">
         <v/>
       </c>
       <c r="D33" t="str">
-        <v>Box B</v>
+        <v>A3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Tissue Culture</v>
+        <v>Glycerol Stocks</v>
       </c>
       <c r="B34" t="str">
-        <v>Position</v>
+        <v>Owner</v>
       </c>
       <c r="C34" t="str">
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>A4</v>
+        <v>Blank = your name</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Kits &amp; Reagents</v>
+        <v>Glycerol Stocks</v>
       </c>
       <c r="B35" t="str">
-        <v>Kit Name</v>
+        <v>Map</v>
       </c>
       <c r="C35" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="D35" t="str">
-        <v>QIAprep Spin Miniprep Kit</v>
+        <v>https://benchling.com/...</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Kits &amp; Reagents</v>
+        <v>Glycerol Stocks</v>
       </c>
       <c r="B36" t="str">
-        <v>Supplier</v>
+        <v>Notes</v>
       </c>
       <c r="C36" t="str">
         <v/>
       </c>
       <c r="D36" t="str">
-        <v>QIAGEN</v>
+        <v>Any extra information</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Kits &amp; Reagents</v>
+        <v>Tissue Culture</v>
       </c>
       <c r="B37" t="str">
-        <v>Catalog #</v>
+        <v>Cell Line</v>
       </c>
       <c r="C37" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="D37" t="str">
-        <v>27104</v>
+        <v>HEK293T</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Kits &amp; Reagents</v>
+        <v>Tissue Culture</v>
       </c>
       <c r="B38" t="str">
-        <v>Qty Left</v>
+        <v>Passage</v>
       </c>
       <c r="C38" t="str">
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>250 preps</v>
+        <v>P12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Kits &amp; Reagents</v>
+        <v>Tissue Culture</v>
       </c>
       <c r="B39" t="str">
-        <v>Expiry</v>
+        <v>Source</v>
       </c>
       <c r="C39" t="str">
         <v/>
       </c>
       <c r="D39" t="str">
-        <v>2027-01-31</v>
+        <v>ATCC CRL-3216</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
+        <v>Tissue Culture</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Liquid N₂ Tank</v>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v>LN2 Tank 1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Tissue Culture</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Rack</v>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v>Rack 3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Tissue Culture</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Box</v>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v>Box B</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Tissue Culture</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Position</v>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v>A4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
         <v>Kits &amp; Reagents</v>
       </c>
-      <c r="B40" t="str">
+      <c r="B44" t="str">
+        <v>Kit Name</v>
+      </c>
+      <c r="C44" t="str">
+        <v>yes</v>
+      </c>
+      <c r="D44" t="str">
+        <v>QIAprep Spin Miniprep Kit</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Kits &amp; Reagents</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Supplier</v>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v>QIAGEN</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Kits &amp; Reagents</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Catalog #</v>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v>27104</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Kits &amp; Reagents</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Qty Left</v>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v>250 preps</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Kits &amp; Reagents</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Expiry</v>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
+        <v>2027-01-31</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Kits &amp; Reagents</v>
+      </c>
+      <c r="B49" t="str">
         <v>Storage</v>
       </c>
-      <c r="C40" t="str">
-        <v/>
-      </c>
-      <c r="D40" t="str">
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49" t="str">
         <v>Room temp, Kit Shelf B</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D49"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -966,35 +1083,67 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:M1"/>
   <cols>
-    <col min="1" max="1" width="17.83203125" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
     <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Strain / Name</v>
+        <v>Serial #</v>
       </c>
       <c r="B1" t="str">
-        <v>Plasmid</v>
+        <v>Description</v>
       </c>
       <c r="C1" t="str">
-        <v>Date Prepared</v>
+        <v>Resistance</v>
       </c>
       <c r="D1" t="str">
+        <v>Sequenced (QC)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Strain</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Freezer (-80°C)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Shelf</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Place on Shelf</v>
+      </c>
+      <c r="I1" t="str">
         <v>Box</v>
       </c>
-      <c r="E1" t="str">
-        <v>Made by</v>
+      <c r="J1" t="str">
+        <v>Position</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Map</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Notes</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/assets/elias-lab-inventory-template.xlsx
+++ b/assets/elias-lab-inventory-template.xlsx
@@ -721,13 +721,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B30" t="str">
-        <v>Shelf</v>
+        <v>Rack_Shelf</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
       <c r="D30" t="str">
-        <v>2</v>
+        <v>R2_S3</v>
       </c>
     </row>
     <row r="31">
@@ -735,7 +735,7 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B31" t="str">
-        <v>Place on Shelf</v>
+        <v>Position on Drawer</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -1092,7 +1092,7 @@
     <col min="5" max="5" width="16.83203125" customWidth="1"/>
     <col min="6" max="6" width="19.83203125" customWidth="1"/>
     <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" customWidth="1"/>
     <col min="9" max="9" width="16.83203125" customWidth="1"/>
     <col min="10" max="10" width="16.83203125" customWidth="1"/>
     <col min="11" max="11" width="16.83203125" customWidth="1"/>
@@ -1120,10 +1120,10 @@
         <v>Freezer (-80°C)</v>
       </c>
       <c r="G1" t="str">
-        <v>Shelf</v>
+        <v>Rack_Shelf</v>
       </c>
       <c r="H1" t="str">
-        <v>Place on Shelf</v>
+        <v>Position on Drawer</v>
       </c>
       <c r="I1" t="str">
         <v>Box</v>

--- a/assets/elias-lab-inventory-template.xlsx
+++ b/assets/elias-lab-inventory-template.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D52"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -623,55 +623,55 @@
         <v>Plasmids</v>
       </c>
       <c r="B23" t="str">
-        <v>Location</v>
+        <v>Freezer</v>
       </c>
       <c r="C23" t="str">
         <v/>
       </c>
       <c r="D23" t="str">
-        <v>-80°C Plasmid Box 1</v>
+        <v>Freezer A</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Glycerol Stocks</v>
+        <v>Plasmids</v>
       </c>
       <c r="B24" t="str">
-        <v>Serial #</v>
+        <v>Box</v>
       </c>
       <c r="C24" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="D24" t="str">
-        <v>GS-0001 (must be unique)</v>
+        <v>Plasmid Box 1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Glycerol Stocks</v>
+        <v>Plasmids</v>
       </c>
       <c r="B25" t="str">
-        <v>Description</v>
+        <v>Position</v>
       </c>
       <c r="C25" t="str">
         <v/>
       </c>
       <c r="D25" t="str">
-        <v>pUC19-HK022 attB, clone 3</v>
+        <v>A3 (or 1-81)</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Glycerol Stocks</v>
+        <v>Plasmids</v>
       </c>
       <c r="B26" t="str">
-        <v>Resistance</v>
+        <v>Location</v>
       </c>
       <c r="C26" t="str">
         <v/>
       </c>
       <c r="D26" t="str">
-        <v>AmpR</v>
+        <v>Any other location detail</v>
       </c>
     </row>
     <row r="27">
@@ -679,13 +679,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B27" t="str">
-        <v>Sequenced (QC)</v>
+        <v>Serial #</v>
       </c>
       <c r="C27" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="D27" t="str">
-        <v>Sequenced with M13F + M13R, correct</v>
+        <v>GS-0001 (must be unique)</v>
       </c>
     </row>
     <row r="28">
@@ -693,13 +693,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B28" t="str">
-        <v>Strain</v>
+        <v>Description</v>
       </c>
       <c r="C28" t="str">
         <v/>
       </c>
       <c r="D28" t="str">
-        <v>DH5α, NEB Stable, Stbl3 or other</v>
+        <v>pUC19-HK022 attB, clone 3</v>
       </c>
     </row>
     <row r="29">
@@ -707,13 +707,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B29" t="str">
-        <v>Freezer (-80°C)</v>
+        <v>Resistance</v>
       </c>
       <c r="C29" t="str">
         <v/>
       </c>
       <c r="D29" t="str">
-        <v>Freezer A</v>
+        <v>AmpR</v>
       </c>
     </row>
     <row r="30">
@@ -721,13 +721,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B30" t="str">
-        <v>Rack_Shelf</v>
+        <v>Sequenced (QC)</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
       <c r="D30" t="str">
-        <v>R2_S3</v>
+        <v>Sequenced with M13F + M13R, correct</v>
       </c>
     </row>
     <row r="31">
@@ -735,13 +735,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B31" t="str">
-        <v>Position on Drawer</v>
+        <v>Strain</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
       <c r="D31" t="str">
-        <v>Left, front</v>
+        <v>DH5α, NEB Stable, Stbl3 or other</v>
       </c>
     </row>
     <row r="32">
@@ -749,13 +749,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B32" t="str">
-        <v>Box</v>
+        <v>Freezer (-80°C)</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>Box G1</v>
+        <v>Freezer A</v>
       </c>
     </row>
     <row r="33">
@@ -763,13 +763,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B33" t="str">
-        <v>Position</v>
+        <v>Rack_Shelf</v>
       </c>
       <c r="C33" t="str">
         <v/>
       </c>
       <c r="D33" t="str">
-        <v>A3</v>
+        <v>R2_S3</v>
       </c>
     </row>
     <row r="34">
@@ -777,13 +777,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B34" t="str">
-        <v>Owner</v>
+        <v>Position on Drawer</v>
       </c>
       <c r="C34" t="str">
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>Blank = your name</v>
+        <v>Left, front</v>
       </c>
     </row>
     <row r="35">
@@ -791,13 +791,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B35" t="str">
-        <v>Map</v>
+        <v>Box</v>
       </c>
       <c r="C35" t="str">
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>https://benchling.com/...</v>
+        <v>Box G1</v>
       </c>
     </row>
     <row r="36">
@@ -805,55 +805,55 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B36" t="str">
-        <v>Notes</v>
+        <v>Position</v>
       </c>
       <c r="C36" t="str">
         <v/>
       </c>
       <c r="D36" t="str">
-        <v>Any extra information</v>
+        <v>A3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Tissue Culture</v>
+        <v>Glycerol Stocks</v>
       </c>
       <c r="B37" t="str">
-        <v>Cell Line</v>
+        <v>Owner</v>
       </c>
       <c r="C37" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="D37" t="str">
-        <v>HEK293T</v>
+        <v>Blank = your name</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Tissue Culture</v>
+        <v>Glycerol Stocks</v>
       </c>
       <c r="B38" t="str">
-        <v>Passage</v>
+        <v>Map</v>
       </c>
       <c r="C38" t="str">
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>P12</v>
+        <v>https://benchling.com/...</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Tissue Culture</v>
+        <v>Glycerol Stocks</v>
       </c>
       <c r="B39" t="str">
-        <v>Source</v>
+        <v>Notes</v>
       </c>
       <c r="C39" t="str">
         <v/>
       </c>
       <c r="D39" t="str">
-        <v>ATCC CRL-3216</v>
+        <v>Any extra information</v>
       </c>
     </row>
     <row r="40">
@@ -861,13 +861,13 @@
         <v>Tissue Culture</v>
       </c>
       <c r="B40" t="str">
-        <v>Liquid N₂ Tank</v>
+        <v>Cell Line</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="D40" t="str">
-        <v>LN2 Tank 1</v>
+        <v>HEK293T</v>
       </c>
     </row>
     <row r="41">
@@ -875,13 +875,13 @@
         <v>Tissue Culture</v>
       </c>
       <c r="B41" t="str">
-        <v>Rack</v>
+        <v>Passage</v>
       </c>
       <c r="C41" t="str">
         <v/>
       </c>
       <c r="D41" t="str">
-        <v>Rack 3</v>
+        <v>P12</v>
       </c>
     </row>
     <row r="42">
@@ -889,13 +889,13 @@
         <v>Tissue Culture</v>
       </c>
       <c r="B42" t="str">
-        <v>Box</v>
+        <v>Source</v>
       </c>
       <c r="C42" t="str">
         <v/>
       </c>
       <c r="D42" t="str">
-        <v>Box B</v>
+        <v>ATCC CRL-3216</v>
       </c>
     </row>
     <row r="43">
@@ -903,55 +903,55 @@
         <v>Tissue Culture</v>
       </c>
       <c r="B43" t="str">
-        <v>Position</v>
+        <v>Liquid N₂ Tank</v>
       </c>
       <c r="C43" t="str">
         <v/>
       </c>
       <c r="D43" t="str">
-        <v>A4</v>
+        <v>LN2 Tank 1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Kits &amp; Reagents</v>
+        <v>Tissue Culture</v>
       </c>
       <c r="B44" t="str">
-        <v>Kit Name</v>
+        <v>Rack</v>
       </c>
       <c r="C44" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="D44" t="str">
-        <v>QIAprep Spin Miniprep Kit</v>
+        <v>Rack 3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Kits &amp; Reagents</v>
+        <v>Tissue Culture</v>
       </c>
       <c r="B45" t="str">
-        <v>Supplier</v>
+        <v>Box</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
       <c r="D45" t="str">
-        <v>QIAGEN</v>
+        <v>Box B</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Kits &amp; Reagents</v>
+        <v>Tissue Culture</v>
       </c>
       <c r="B46" t="str">
-        <v>Catalog #</v>
+        <v>Position</v>
       </c>
       <c r="C46" t="str">
         <v/>
       </c>
       <c r="D46" t="str">
-        <v>27104</v>
+        <v>A4</v>
       </c>
     </row>
     <row r="47">
@@ -959,13 +959,13 @@
         <v>Kits &amp; Reagents</v>
       </c>
       <c r="B47" t="str">
-        <v>Qty Left</v>
+        <v>Kit Name</v>
       </c>
       <c r="C47" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="D47" t="str">
-        <v>250 preps</v>
+        <v>QIAprep Spin Miniprep Kit</v>
       </c>
     </row>
     <row r="48">
@@ -973,13 +973,13 @@
         <v>Kits &amp; Reagents</v>
       </c>
       <c r="B48" t="str">
-        <v>Expiry</v>
+        <v>Supplier</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
       <c r="D48" t="str">
-        <v>2027-01-31</v>
+        <v>QIAGEN</v>
       </c>
     </row>
     <row r="49">
@@ -987,18 +987,60 @@
         <v>Kits &amp; Reagents</v>
       </c>
       <c r="B49" t="str">
+        <v>Catalog #</v>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49" t="str">
+        <v>27104</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Kits &amp; Reagents</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Qty Left</v>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v>250 preps</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Kits &amp; Reagents</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Expiry</v>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51" t="str">
+        <v>2027-01-31</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Kits &amp; Reagents</v>
+      </c>
+      <c r="B52" t="str">
         <v>Storage</v>
       </c>
-      <c r="C49" t="str">
-        <v/>
-      </c>
-      <c r="D49" t="str">
+      <c r="C52" t="str">
+        <v/>
+      </c>
+      <c r="D52" t="str">
         <v>Room temp, Kit Shelf B</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1048,13 +1090,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:H1"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="3" width="16.83203125" customWidth="1"/>
     <col min="4" max="4" width="16.83203125" customWidth="1"/>
     <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1071,12 +1116,21 @@
         <v>Resistance</v>
       </c>
       <c r="E1" t="str">
+        <v>Freezer</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Box</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Position</v>
+      </c>
+      <c r="H1" t="str">
         <v>Location</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/assets/elias-lab-inventory-template.xlsx
+++ b/assets/elias-lab-inventory-template.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D58"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -623,13 +623,13 @@
         <v>Plasmids</v>
       </c>
       <c r="B23" t="str">
-        <v>Freezer</v>
+        <v>Conc.</v>
       </c>
       <c r="C23" t="str">
         <v/>
       </c>
       <c r="D23" t="str">
-        <v>Freezer A</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -637,13 +637,13 @@
         <v>Plasmids</v>
       </c>
       <c r="B24" t="str">
-        <v>Box</v>
+        <v>Owner</v>
       </c>
       <c r="C24" t="str">
         <v/>
       </c>
       <c r="D24" t="str">
-        <v>Plasmid Box 1</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -651,13 +651,13 @@
         <v>Plasmids</v>
       </c>
       <c r="B25" t="str">
-        <v>Position</v>
+        <v>Freezer</v>
       </c>
       <c r="C25" t="str">
         <v/>
       </c>
       <c r="D25" t="str">
-        <v>A3 (or 1-81)</v>
+        <v>Freezer A</v>
       </c>
     </row>
     <row r="26">
@@ -665,41 +665,41 @@
         <v>Plasmids</v>
       </c>
       <c r="B26" t="str">
-        <v>Location</v>
+        <v>Box</v>
       </c>
       <c r="C26" t="str">
         <v/>
       </c>
       <c r="D26" t="str">
-        <v>Any other location detail</v>
+        <v>Plasmid Box 1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Glycerol Stocks</v>
+        <v>Plasmids</v>
       </c>
       <c r="B27" t="str">
-        <v>Serial #</v>
+        <v>Position</v>
       </c>
       <c r="C27" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="D27" t="str">
-        <v>GS-0001 (must be unique)</v>
+        <v>A3 (or 1-81)</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Glycerol Stocks</v>
+        <v>Plasmids</v>
       </c>
       <c r="B28" t="str">
-        <v>Description</v>
+        <v>Location</v>
       </c>
       <c r="C28" t="str">
         <v/>
       </c>
       <c r="D28" t="str">
-        <v>pUC19-HK022 attB, clone 3</v>
+        <v>Any other location detail</v>
       </c>
     </row>
     <row r="29">
@@ -707,13 +707,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B29" t="str">
-        <v>Resistance</v>
+        <v>Serial #</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="D29" t="str">
-        <v>AmpR</v>
+        <v>GS-0001 (must be unique)</v>
       </c>
     </row>
     <row r="30">
@@ -721,13 +721,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B30" t="str">
-        <v>Sequenced (QC)</v>
+        <v>Description</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
       <c r="D30" t="str">
-        <v>Sequenced with M13F + M13R, correct</v>
+        <v>pUC19-HK022 attB, clone 3</v>
       </c>
     </row>
     <row r="31">
@@ -735,13 +735,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B31" t="str">
-        <v>Strain</v>
+        <v>Resistance</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
       <c r="D31" t="str">
-        <v>DH5α, NEB Stable, Stbl3 or other</v>
+        <v>AmpR</v>
       </c>
     </row>
     <row r="32">
@@ -749,13 +749,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B32" t="str">
-        <v>Freezer (-80°C)</v>
+        <v>Sequenced (QC)</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>Freezer A</v>
+        <v>Sequenced with M13F + M13R, correct</v>
       </c>
     </row>
     <row r="33">
@@ -763,13 +763,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B33" t="str">
-        <v>Rack_Shelf</v>
+        <v>Strain</v>
       </c>
       <c r="C33" t="str">
         <v/>
       </c>
       <c r="D33" t="str">
-        <v>R2_S3</v>
+        <v>DH5α, NEB Stable, Stbl3 or other</v>
       </c>
     </row>
     <row r="34">
@@ -777,13 +777,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B34" t="str">
-        <v>Position on Drawer</v>
+        <v>Freezer (-80°C)</v>
       </c>
       <c r="C34" t="str">
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>Left, front</v>
+        <v>Freezer A</v>
       </c>
     </row>
     <row r="35">
@@ -791,13 +791,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B35" t="str">
-        <v>Box</v>
+        <v>Rack_Shelf</v>
       </c>
       <c r="C35" t="str">
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>Box G1</v>
+        <v>R2_S3</v>
       </c>
     </row>
     <row r="36">
@@ -805,13 +805,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B36" t="str">
-        <v>Position</v>
+        <v>Position on Drawer</v>
       </c>
       <c r="C36" t="str">
         <v/>
       </c>
       <c r="D36" t="str">
-        <v>A3</v>
+        <v>Left, front</v>
       </c>
     </row>
     <row r="37">
@@ -819,13 +819,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B37" t="str">
-        <v>Owner</v>
+        <v>Box</v>
       </c>
       <c r="C37" t="str">
         <v/>
       </c>
       <c r="D37" t="str">
-        <v>Blank = your name</v>
+        <v>Box G1</v>
       </c>
     </row>
     <row r="38">
@@ -833,13 +833,13 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B38" t="str">
-        <v>Map</v>
+        <v>Position</v>
       </c>
       <c r="C38" t="str">
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>https://benchling.com/...</v>
+        <v>A3</v>
       </c>
     </row>
     <row r="39">
@@ -847,41 +847,41 @@
         <v>Glycerol Stocks</v>
       </c>
       <c r="B39" t="str">
-        <v>Notes</v>
+        <v>Owner</v>
       </c>
       <c r="C39" t="str">
         <v/>
       </c>
       <c r="D39" t="str">
-        <v>Any extra information</v>
+        <v>Blank = your name</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Tissue Culture</v>
+        <v>Glycerol Stocks</v>
       </c>
       <c r="B40" t="str">
-        <v>Cell Line</v>
+        <v>Map</v>
       </c>
       <c r="C40" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="D40" t="str">
-        <v>HEK293T</v>
+        <v>https://benchling.com/...</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tissue Culture</v>
+        <v>Glycerol Stocks</v>
       </c>
       <c r="B41" t="str">
-        <v>Passage</v>
+        <v>Notes</v>
       </c>
       <c r="C41" t="str">
         <v/>
       </c>
       <c r="D41" t="str">
-        <v>P12</v>
+        <v>Any extra information</v>
       </c>
     </row>
     <row r="42">
@@ -889,13 +889,13 @@
         <v>Tissue Culture</v>
       </c>
       <c r="B42" t="str">
-        <v>Source</v>
+        <v>Cell Line</v>
       </c>
       <c r="C42" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="D42" t="str">
-        <v>ATCC CRL-3216</v>
+        <v>HEK293T</v>
       </c>
     </row>
     <row r="43">
@@ -903,13 +903,13 @@
         <v>Tissue Culture</v>
       </c>
       <c r="B43" t="str">
-        <v>Liquid N₂ Tank</v>
+        <v>Passage</v>
       </c>
       <c r="C43" t="str">
         <v/>
       </c>
       <c r="D43" t="str">
-        <v>LN2 Tank 1</v>
+        <v>P12</v>
       </c>
     </row>
     <row r="44">
@@ -917,13 +917,13 @@
         <v>Tissue Culture</v>
       </c>
       <c r="B44" t="str">
-        <v>Rack</v>
+        <v>Cells / Vial</v>
       </c>
       <c r="C44" t="str">
         <v/>
       </c>
       <c r="D44" t="str">
-        <v>Rack 3</v>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -931,13 +931,13 @@
         <v>Tissue Culture</v>
       </c>
       <c r="B45" t="str">
-        <v>Box</v>
+        <v>Source</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
       <c r="D45" t="str">
-        <v>Box B</v>
+        <v>ATCC CRL-3216</v>
       </c>
     </row>
     <row r="46">
@@ -945,102 +945,186 @@
         <v>Tissue Culture</v>
       </c>
       <c r="B46" t="str">
-        <v>Position</v>
+        <v>Growth Media</v>
       </c>
       <c r="C46" t="str">
         <v/>
       </c>
       <c r="D46" t="str">
-        <v>A4</v>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Kits &amp; Reagents</v>
+        <v>Tissue Culture</v>
       </c>
       <c r="B47" t="str">
-        <v>Kit Name</v>
+        <v>Banking Media</v>
       </c>
       <c r="C47" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="D47" t="str">
-        <v>QIAprep Spin Miniprep Kit</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Kits &amp; Reagents</v>
+        <v>Tissue Culture</v>
       </c>
       <c r="B48" t="str">
-        <v>Supplier</v>
+        <v>Liquid N₂ Tank</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
       <c r="D48" t="str">
-        <v>QIAGEN</v>
+        <v>LN2 Tank 1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Kits &amp; Reagents</v>
+        <v>Tissue Culture</v>
       </c>
       <c r="B49" t="str">
-        <v>Catalog #</v>
+        <v>Rack</v>
       </c>
       <c r="C49" t="str">
         <v/>
       </c>
       <c r="D49" t="str">
-        <v>27104</v>
+        <v>Rack 3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Kits &amp; Reagents</v>
+        <v>Tissue Culture</v>
       </c>
       <c r="B50" t="str">
-        <v>Qty Left</v>
+        <v>Box</v>
       </c>
       <c r="C50" t="str">
         <v/>
       </c>
       <c r="D50" t="str">
-        <v>250 preps</v>
+        <v>Box B</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Kits &amp; Reagents</v>
+        <v>Tissue Culture</v>
       </c>
       <c r="B51" t="str">
-        <v>Expiry</v>
+        <v>Position</v>
       </c>
       <c r="C51" t="str">
         <v/>
       </c>
       <c r="D51" t="str">
-        <v>2027-01-31</v>
+        <v>A4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
+        <v>Tissue Culture</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="C52" t="str">
+        <v/>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
         <v>Kits &amp; Reagents</v>
       </c>
-      <c r="B52" t="str">
+      <c r="B53" t="str">
+        <v>Kit Name</v>
+      </c>
+      <c r="C53" t="str">
+        <v>yes</v>
+      </c>
+      <c r="D53" t="str">
+        <v>QIAprep Spin Miniprep Kit</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Kits &amp; Reagents</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Supplier</v>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54" t="str">
+        <v>QIAGEN</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Kits &amp; Reagents</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Catalog #</v>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55" t="str">
+        <v>27104</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Kits &amp; Reagents</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Qty Left</v>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v>250 preps</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Kits &amp; Reagents</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Expiry</v>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v>2027-01-31</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Kits &amp; Reagents</v>
+      </c>
+      <c r="B58" t="str">
         <v>Storage</v>
       </c>
-      <c r="C52" t="str">
-        <v/>
-      </c>
-      <c r="D52" t="str">
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
         <v>Room temp, Kit Shelf B</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D58"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1090,7 +1174,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:J1"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1100,6 +1184,8 @@
     <col min="6" max="6" width="16.83203125" customWidth="1"/>
     <col min="7" max="7" width="16.83203125" customWidth="1"/>
     <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1116,21 +1202,27 @@
         <v>Resistance</v>
       </c>
       <c r="E1" t="str">
+        <v>Conc.</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="G1" t="str">
         <v>Freezer</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>Box</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>Position</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>Location</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1204,15 +1296,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:K1"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
     <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1223,24 +1319,36 @@
         <v>Passage</v>
       </c>
       <c r="C1" t="str">
+        <v>Cells / Vial</v>
+      </c>
+      <c r="D1" t="str">
         <v>Source</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
+        <v>Growth Media</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Banking Media</v>
+      </c>
+      <c r="G1" t="str">
         <v>Liquid N₂ Tank</v>
       </c>
-      <c r="E1" t="str">
+      <c r="H1" t="str">
         <v>Rack</v>
       </c>
-      <c r="F1" t="str">
+      <c r="I1" t="str">
         <v>Box</v>
       </c>
-      <c r="G1" t="str">
+      <c r="J1" t="str">
         <v>Position</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Notes</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1"/>
   </ignoredErrors>
 </worksheet>
 </file>
